--- a/insurance_forms/039_homeowners_insurance_form_template--insurance_forms.xlsx
+++ b/insurance_forms/039_homeowners_insurance_form_template--insurance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'duplex'}</t>
+          <t>duplex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Duplex'}</t>
+          <t>Duplex</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'triplex'}</t>
+          <t>triplex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Triplex'}</t>
+          <t>Triplex</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fourplex'}</t>
+          <t>fourplex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fourplex'}</t>
+          <t>Fourplex</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'liability'}</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Liability'}</t>
+          <t>Liability</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'comprehensive'}</t>
+          <t>comprehensive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Comprehensive'}</t>
+          <t>Comprehensive</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'collision'}</t>
+          <t>collision</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Collision'}</t>
+          <t>Collision</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'tertiary'}</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Tertiary'}</t>
+          <t>Tertiary</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'50/100'}</t>
+          <t>50/100</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '50/100'}</t>
+          <t>50/100</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'75/150'}</t>
+          <t>75/150</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': '75/150'}</t>
+          <t>75/150</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'125/250'}</t>
+          <t>125/250</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': '125/250'}</t>
+          <t>125/250</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_50}</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 50}</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_100}</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 100}</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_10000}</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 10000}</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_50000}</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 50000}</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_100000}</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 100000}</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'bi-monthly'}</t>
+          <t>bi-monthly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Bi-Monthly'}</t>
+          <t>Bi-Monthly</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_1950}</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 1950}</t>
+          <t>1950</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_1960}</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 1960}</t>
+          <t>1960</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_1970}</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 1970}</t>
+          <t>1970</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_1980}</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 1980}</t>
+          <t>1980</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_1990}</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 1990}</t>
+          <t>1990</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_2000}</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 2000}</t>
+          <t>2000</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_2010}</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 2010}</t>
+          <t>2010</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
